--- a/dev/CodeSystem-PSGC.xlsx
+++ b/dev/CodeSystem-PSGC.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T05:11:07+00:00</t>
+    <t>2026-03-16T07:24:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/CodeSystem-PSGC.xlsx
+++ b/dev/CodeSystem-PSGC.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T07:24:26+00:00</t>
+    <t>2026-03-16T20:48:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/CodeSystem-PSGC.xlsx
+++ b/dev/CodeSystem-PSGC.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T20:48:05+00:00</t>
+    <t>2026-03-16T20:59:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/CodeSystem-PSGC.xlsx
+++ b/dev/CodeSystem-PSGC.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T20:59:47+00:00</t>
+    <t>2026-03-16T21:16:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/CodeSystem-PSGC.xlsx
+++ b/dev/CodeSystem-PSGC.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T21:16:15+00:00</t>
+    <t>2026-03-16T21:44:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/CodeSystem-PSGC.xlsx
+++ b/dev/CodeSystem-PSGC.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T21:44:19+00:00</t>
+    <t>2026-03-16T21:58:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/CodeSystem-PSGC.xlsx
+++ b/dev/CodeSystem-PSGC.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T21:58:37+00:00</t>
+    <t>2026-03-16T22:06:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/CodeSystem-PSGC.xlsx
+++ b/dev/CodeSystem-PSGC.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T22:06:54+00:00</t>
+    <t>2026-03-16T22:26:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/CodeSystem-PSGC.xlsx
+++ b/dev/CodeSystem-PSGC.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T22:26:22+00:00</t>
+    <t>2026-03-19T20:53:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/CodeSystem-PSGC.xlsx
+++ b/dev/CodeSystem-PSGC.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-19T20:53:49+00:00</t>
+    <t>2026-03-19T21:27:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/CodeSystem-PSGC.xlsx
+++ b/dev/CodeSystem-PSGC.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-19T21:27:42+00:00</t>
+    <t>2026-04-08T04:20:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/CodeSystem-PSGC.xlsx
+++ b/dev/CodeSystem-PSGC.xlsx
@@ -24,13 +24,13 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://doh.gov.ph/fhir/ph-core/CodeSystem/PSGC</t>
+    <t>https://psa.gov.ph/classification/psgc</t>
   </si>
   <si>
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T04:20:57+00:00</t>
+    <t>2026-04-10T05:32:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/CodeSystem-PSGC.xlsx
+++ b/dev/CodeSystem-PSGC.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-10T05:32:03+00:00</t>
+    <t>2026-04-10T05:44:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/CodeSystem-PSGC.xlsx
+++ b/dev/CodeSystem-PSGC.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="98">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-10T05:44:36+00:00</t>
+    <t>2026-05-26T03:51:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -120,7 +120,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>22</t>
+    <t>29</t>
   </si>
   <si>
     <t>Level</t>
@@ -138,6 +138,24 @@
     <t>1</t>
   </si>
   <si>
+    <t>1300000000</t>
+  </si>
+  <si>
+    <t>National Capital Region</t>
+  </si>
+  <si>
+    <t>1380600000</t>
+  </si>
+  <si>
+    <t>City of Manila</t>
+  </si>
+  <si>
+    <t>1339000003</t>
+  </si>
+  <si>
+    <t>Ermita</t>
+  </si>
+  <si>
     <t>1380100001</t>
   </si>
   <si>
@@ -268,6 +286,27 @@
   </si>
   <si>
     <t>Occidental Mindoro</t>
+  </si>
+  <si>
+    <t>0100000000</t>
+  </si>
+  <si>
+    <t>Ilocos Region</t>
+  </si>
+  <si>
+    <t>0133000000</t>
+  </si>
+  <si>
+    <t>0133070000</t>
+  </si>
+  <si>
+    <t>Bauang</t>
+  </si>
+  <si>
+    <t>0133070250</t>
+  </si>
+  <si>
+    <t>Paringao</t>
   </si>
 </sst>
 </file>
@@ -577,7 +616,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -858,6 +897,90 @@
       </c>
       <c r="D23" s="2"/>
     </row>
+    <row r="24">
+      <c r="A24" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B24" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="C24" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="D24" s="2"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B25" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="C25" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="D25" s="2"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B26" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="C26" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="D26" s="2"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B27" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="C27" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="D27" s="2"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B28" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="C28" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="D28" s="2"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B29" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="C29" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="D29" s="2"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B30" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="C30" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="D30" s="2"/>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/dev/CodeSystem-PSGC.xlsx
+++ b/dev/CodeSystem-PSGC.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-26T03:51:01+00:00</t>
+    <t>2026-05-26T04:00:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/CodeSystem-PSGC.xlsx
+++ b/dev/CodeSystem-PSGC.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-26T04:00:40+00:00</t>
+    <t>2026-05-26T04:36:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
